--- a/ENTREGA_FINAL/Atlas tracking/1st_round_-_with_flavio-210720261102.xlsx
+++ b/ENTREGA_FINAL/Atlas tracking/1st_round_-_with_flavio-210720261102.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AE14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -490,6 +490,9 @@
       <c r="AD1" t="str">
         <v>2026-07-20</v>
       </c>
+      <c r="AE1" t="str">
+        <v>2026-07-27</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -582,6 +585,9 @@
       <c r="AD2">
         <v>45.7</v>
       </c>
+      <c r="AE2">
+        <v>48.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -674,6 +680,9 @@
       <c r="AD3">
         <v>38</v>
       </c>
+      <c r="AE3">
+        <v>36.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -766,189 +775,198 @@
       <c r="AD4">
         <v>6.9</v>
       </c>
+      <c r="AE4">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Romeu Zema</v>
+        <v>Ronaldo Caiado</v>
       </c>
       <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>5.6</v>
+      </c>
+      <c r="D5">
+        <v>5.1</v>
+      </c>
+      <c r="E5">
+        <v>4.6</v>
+      </c>
+      <c r="F5">
+        <v>3.8</v>
+      </c>
+      <c r="G5">
+        <v>3.7</v>
+      </c>
+      <c r="H5">
+        <v>3.7</v>
+      </c>
+      <c r="I5">
+        <v>2.8</v>
+      </c>
+      <c r="J5">
+        <v>2.3</v>
+      </c>
+      <c r="K5">
+        <v>2.1</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2.7</v>
+      </c>
+      <c r="N5">
+        <v>2.5</v>
+      </c>
+      <c r="O5">
+        <v>2.5</v>
+      </c>
+      <c r="P5">
+        <v>2.5</v>
+      </c>
+      <c r="Q5">
         <v>1.8</v>
       </c>
-      <c r="C5">
-        <v>2.1</v>
-      </c>
-      <c r="D5">
-        <v>2.1</v>
-      </c>
-      <c r="E5">
-        <v>2.2</v>
-      </c>
-      <c r="F5">
+      <c r="R5">
+        <v>1.6</v>
+      </c>
+      <c r="S5">
+        <v>1.9</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>1.9</v>
+      </c>
+      <c r="V5">
+        <v>1.9</v>
+      </c>
+      <c r="W5">
         <v>1.8</v>
       </c>
-      <c r="G5">
-        <v>2.1</v>
-      </c>
-      <c r="H5">
+      <c r="X5">
         <v>2.4</v>
       </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
+      <c r="Y5">
+        <v>2.9</v>
+      </c>
+      <c r="Z5">
+        <v>2.4</v>
+      </c>
+      <c r="AA5">
         <v>2.6</v>
       </c>
-      <c r="K5">
-        <v>2.3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-      <c r="O5">
-        <v>2.9</v>
-      </c>
-      <c r="P5">
-        <v>3.1</v>
-      </c>
-      <c r="Q5">
-        <v>2.7</v>
-      </c>
-      <c r="R5">
-        <v>3.8</v>
-      </c>
-      <c r="S5">
-        <v>4.2</v>
-      </c>
-      <c r="T5">
-        <v>4.4</v>
-      </c>
-      <c r="U5">
-        <v>4.4</v>
-      </c>
-      <c r="V5">
-        <v>4.9</v>
-      </c>
-      <c r="W5">
-        <v>2.9</v>
-      </c>
-      <c r="X5">
-        <v>2.5</v>
-      </c>
-      <c r="Y5">
+      <c r="AB5">
         <v>2.6</v>
-      </c>
-      <c r="Z5">
-        <v>2.3</v>
-      </c>
-      <c r="AA5">
-        <v>2.5</v>
-      </c>
-      <c r="AB5">
-        <v>3.3</v>
       </c>
       <c r="AC5">
         <v>3</v>
       </c>
       <c r="AD5">
-        <v>2.7</v>
+        <v>2.6</v>
+      </c>
+      <c r="AE5">
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Ronaldo Caiado</v>
+        <v>Romeu Zema</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="C6">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="D6">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="E6">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="F6">
+        <v>1.8</v>
+      </c>
+      <c r="G6">
+        <v>2.1</v>
+      </c>
+      <c r="H6">
+        <v>2.4</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>2.6</v>
+      </c>
+      <c r="K6">
+        <v>2.3</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>2.9</v>
+      </c>
+      <c r="P6">
+        <v>3.1</v>
+      </c>
+      <c r="Q6">
+        <v>2.7</v>
+      </c>
+      <c r="R6">
         <v>3.8</v>
       </c>
-      <c r="G6">
-        <v>3.7</v>
-      </c>
-      <c r="H6">
-        <v>3.7</v>
-      </c>
-      <c r="I6">
-        <v>2.8</v>
-      </c>
-      <c r="J6">
+      <c r="S6">
+        <v>4.2</v>
+      </c>
+      <c r="T6">
+        <v>4.4</v>
+      </c>
+      <c r="U6">
+        <v>4.4</v>
+      </c>
+      <c r="V6">
+        <v>4.9</v>
+      </c>
+      <c r="W6">
+        <v>2.9</v>
+      </c>
+      <c r="X6">
+        <v>2.5</v>
+      </c>
+      <c r="Y6">
+        <v>2.6</v>
+      </c>
+      <c r="Z6">
         <v>2.3</v>
       </c>
-      <c r="K6">
-        <v>2.1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>2.7</v>
-      </c>
-      <c r="N6">
+      <c r="AA6">
         <v>2.5</v>
       </c>
-      <c r="O6">
-        <v>2.5</v>
-      </c>
-      <c r="P6">
-        <v>2.5</v>
-      </c>
-      <c r="Q6">
-        <v>1.8</v>
-      </c>
-      <c r="R6">
-        <v>1.6</v>
-      </c>
-      <c r="S6">
-        <v>1.9</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
-      </c>
-      <c r="U6">
-        <v>1.9</v>
-      </c>
-      <c r="V6">
-        <v>1.9</v>
-      </c>
-      <c r="W6">
-        <v>1.8</v>
-      </c>
-      <c r="X6">
-        <v>2.4</v>
-      </c>
-      <c r="Y6">
-        <v>2.9</v>
-      </c>
-      <c r="Z6">
-        <v>2.4</v>
-      </c>
-      <c r="AA6">
-        <v>2.6</v>
-      </c>
       <c r="AB6">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AC6">
         <v>3</v>
       </c>
       <c r="AD6">
-        <v>2.6</v>
+        <v>2.7</v>
+      </c>
+      <c r="AE6">
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -1042,6 +1060,9 @@
       <c r="AD7">
         <v>1.9</v>
       </c>
+      <c r="AE7">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1166,6 +1187,9 @@
       <c r="AD9">
         <v>0.8</v>
       </c>
+      <c r="AE9">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1341,7 +1365,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE14"/>
   </ignoredErrors>
 </worksheet>
 </file>